--- a/output/pdf_financials_xlsx/IRV.xlsx
+++ b/output/pdf_financials_xlsx/IRV.xlsx
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>9.807043999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>10.077948</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>10.292492</v>
       </c>
     </row>
     <row r="93">
@@ -3105,7 +3105,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3229,7 +3233,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>9.807043999999999</v>
       </c>

--- a/output/pdf_financials_xlsx/IRV.xlsx
+++ b/output/pdf_financials_xlsx/IRV.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.248616</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.043562</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007367</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.185614</v>
+        <v>-2.43423</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.038518</v>
+        <v>-5.08208</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.622416</v>
+        <v>-1.629783</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.017863</v>
+        <v>-2.266479</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.880183</v>
+        <v>-4.923745</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.457896</v>
+        <v>-1.465263</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.7349</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.087356</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.087988</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.7349</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.087356</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.087988</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.849723</v>
+        <v>0.114823</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.252494</v>
+        <v>0.165138</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.240842</v>
+        <v>0.152854</v>
       </c>
     </row>
     <row r="49">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">

--- a/output/pdf_financials_xlsx/IRV.xlsx
+++ b/output/pdf_financials_xlsx/IRV.xlsx
@@ -535,7 +535,7 @@
         <v>0.6865560000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.929639</v>
+        <v>0.935639</v>
       </c>
     </row>
     <row r="8">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.133911</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.110944</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.097666</v>
       </c>
     </row>
     <row r="71">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.133911</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.110944</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.097666</v>
       </c>
     </row>
     <row r="72">
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.133911</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.70367</v>
+        <v>0.592726</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.699922</v>
+        <v>0.602256</v>
       </c>
     </row>
     <row r="76">
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.00165543874545655</v>
+        <v>0.004358047192184158</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.001014999819914813</v>
+        <v>0.003435274929434639</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.0006706181864223274</v>
+        <v>0.002642219504758361</v>
       </c>
     </row>
     <row r="81">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.456382</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003453</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.049176</v>
       </c>
     </row>
     <row r="112">
@@ -2579,13 +2579,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.456382</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003453</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.049176</v>
       </c>
     </row>
     <row r="135">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.8859399999999999</v>
+        <v>-1.342322</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.292566</v>
+        <v>-1.296019</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.424968</v>
+        <v>-0.474144</v>
       </c>
     </row>
   </sheetData>
@@ -2952,7 +2952,11 @@
           <t>Lease liabilities (Note 6)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.133911</v>
       </c>
@@ -3736,7 +3740,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>-0.456382</v>
       </c>
@@ -4065,7 +4073,11 @@
           <t>Director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
